--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS6400_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS6400_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1229,6 +1229,157 @@
       <c r="AQ5" t="inlineStr">
         <is>
           <t>FS6400-08-12-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FS6400-24-24-O</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="S6" t="n">
+        <v>45</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.4676</v>
+      </c>
+      <c r="V6" t="n">
+        <v>60</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.12505</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5296</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.0445</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>FS6400-24-24-O</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ORFS Straight Thread Connector (male face seal x male ORB), 1 7/8-12 (male ORB) (SAE J1926 stud, FS part) x 2-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>FS6400</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (male ORB) (SAE J1926 stud, FS part)</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Air-Way FF6400 (s14, double-pass 2026-10-15, parts.air-way.com/api/series/14, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p5 FS6400-24-24-O (ORFS-p005-t03) | MODEL: L8 face -&gt; ORB tip, L9 face -&gt; hex ORB-side face, hex S5, bores D20 (ORB side) / D1 (face-seal side): review table (Air-Way, staged FS table; OMi website list decides the parts); hex = L9 - the face-seal end; bore step at the hex mid-plane (ASSUMPTION, as 2403 / 6400); hex end chamfers NOT modelled; FS6400-L (long, Air-Way L32 / L31) not folded in yet: no shape source for where the extra length goes (needs BRENNAN_FS6400-L-08-08-O); male SAE ORB stud on an FS part: thread major, groove dia and width = the ORB end library of the dash (6401 / 6405 / 6410 rows); stud length tip -&gt; hex face = Air-Way (L8 - L9) and the extra length over the library end is THREAD (measured on the Brennan FS6400-08-08-O pilot: undercut 0.660 x 0.094 = ORB -08, thread to 0.457 from the tip; single size - ASSUMED for the other dashes); tip chamfer and O-ring not modelled; male O-ring face-seal end (SAE J1453): thread = the face-seal thread of the dash (Air-Way callout = Brennan ORFS catalog); face O-ring groove (inner / outer dia, depth), land, 45deg nose chamfer, thread length, 60deg flank, relief and end length measured on the Brennan pilot of that dash (Brennan FS2403-24-24 (both ends; fsmeasure.measure_fsm, orfs_steps2_20261020 ends_survey); single manufacturer - Air-Way 3D models not yet measured, Q-FS-2NDSHAPE); groove drawn rectangular (its outer bottom corner is hidden under the O-ring Brennan fuses into the solid - ASSUMPTION); O-ring not modelled (separate FS4000 part)</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Air-Way FF6400 (built to Air-Way); Brennan p5 DIFFERS (up to 0.092 in): overall length L8=2.22 vs Brennan L LGTH=2.128 | OMi parts file row 5550 (no dimensions)</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>FS6400-24-24-O</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS6400_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS6400_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
